--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/NEW_MEXICO_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/NEW_MEXICO_2018.xlsx
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C162">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C241">
